--- a/dataset_t6_grouped/results2/G5/G5_T2372_W0066F0002T0006Z000C1N18_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T2372_W0066F0002T0006Z000C1N18_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>9.610870820072549</v>
+        <v>1.561766508261789</v>
       </c>
       <c r="D2" t="n">
-        <v>9.545885439480729</v>
+        <v>1.551206383915618</v>
       </c>
       <c r="E2" t="n">
-        <v>10.80676900801926</v>
+        <v>1.75609996380313</v>
       </c>
       <c r="F2" t="n">
-        <v>10.61422665758912</v>
+        <v>1.724811831858233</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>32.08971679202085</v>
+        <v>5.214578978703389</v>
       </c>
       <c r="D3" t="n">
-        <v>31.28774658584017</v>
+        <v>5.084258820199027</v>
       </c>
       <c r="E3" t="n">
-        <v>10.80676900801926</v>
+        <v>1.75609996380313</v>
       </c>
       <c r="F3" t="n">
-        <v>10.61422665758912</v>
+        <v>1.724811831858233</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>8.743920831693375</v>
+        <v>1.420887135150174</v>
       </c>
       <c r="D4" t="n">
-        <v>8.069883626704833</v>
+        <v>1.311356089339535</v>
       </c>
       <c r="E4" t="n">
-        <v>10.80676900801926</v>
+        <v>1.75609996380313</v>
       </c>
       <c r="F4" t="n">
-        <v>10.61422665758912</v>
+        <v>1.724811831858233</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
